--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9188484F-4B73-438F-8A9C-C9FA07A7CCAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72B626EF-306E-4E3C-B3E9-51B5C57AA106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72B626EF-306E-4E3C-B3E9-51B5C57AA106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98E323D7-B07C-411F-AEC8-EAB89C5EC33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98E323D7-B07C-411F-AEC8-EAB89C5EC33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2E5B9C2-C959-4AFA-B8DB-4AEA764CE373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2E5B9C2-C959-4AFA-B8DB-4AEA764CE373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE40E277-AF59-4077-BBE2-A868F4241F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE40E277-AF59-4077-BBE2-A868F4241F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C37E66D1-9522-469F-8E3B-ECF2C09F2C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C37E66D1-9522-469F-8E3B-ECF2C09F2C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E750DB5-2972-45DF-865D-40062D80DF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E750DB5-2972-45DF-865D-40062D80DF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{067250AF-0C85-4F80-B0A2-04F67E562275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{067250AF-0C85-4F80-B0A2-04F67E562275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5478CAFA-21E8-4B6A-9E44-9A1EA7D273C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5478CAFA-21E8-4B6A-9E44-9A1EA7D273C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25E9AED4-F535-4D37-AAFF-434531C9FBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
